--- a/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_6.xlsx
+++ b/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Panel_D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_D" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN97"/>
+  <dimension ref="A1:BQ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -445,58 +445,61 @@
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="37" customWidth="1" min="14" max="14"/>
-    <col width="62" customWidth="1" min="15" max="15"/>
-    <col width="31" customWidth="1" min="16" max="16"/>
+    <col width="57" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="62" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="62" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="25" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="27" customWidth="1" min="28" max="28"/>
-    <col width="27" customWidth="1" min="29" max="29"/>
-    <col width="27" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="25" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="30" max="30"/>
     <col width="27" customWidth="1" min="31" max="31"/>
-    <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
-    <col width="28" customWidth="1" min="34" max="34"/>
-    <col width="28" customWidth="1" min="35" max="35"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="27" customWidth="1" min="34" max="34"/>
+    <col width="31" customWidth="1" min="35" max="35"/>
     <col width="28" customWidth="1" min="36" max="36"/>
-    <col width="34" customWidth="1" min="37" max="37"/>
-    <col width="31" customWidth="1" min="38" max="38"/>
-    <col width="31" customWidth="1" min="39" max="39"/>
-    <col width="31" customWidth="1" min="40" max="40"/>
+    <col width="28" customWidth="1" min="37" max="37"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="39" max="39"/>
+    <col width="34" customWidth="1" min="40" max="40"/>
     <col width="31" customWidth="1" min="41" max="41"/>
     <col width="31" customWidth="1" min="42" max="42"/>
-    <col width="28" customWidth="1" min="43" max="43"/>
-    <col width="28" customWidth="1" min="44" max="44"/>
-    <col width="28" customWidth="1" min="45" max="45"/>
+    <col width="31" customWidth="1" min="43" max="43"/>
+    <col width="31" customWidth="1" min="44" max="44"/>
+    <col width="31" customWidth="1" min="45" max="45"/>
     <col width="28" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
-    <col width="25" customWidth="1" min="48" max="48"/>
-    <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="25" customWidth="1" min="50" max="50"/>
+    <col width="28" customWidth="1" min="48" max="48"/>
+    <col width="28" customWidth="1" min="49" max="49"/>
+    <col width="28" customWidth="1" min="50" max="50"/>
     <col width="25" customWidth="1" min="51" max="51"/>
-    <col width="29" customWidth="1" min="52" max="52"/>
-    <col width="26" customWidth="1" min="53" max="53"/>
-    <col width="26" customWidth="1" min="54" max="54"/>
-    <col width="26" customWidth="1" min="55" max="55"/>
+    <col width="25" customWidth="1" min="52" max="52"/>
+    <col width="25" customWidth="1" min="53" max="53"/>
+    <col width="25" customWidth="1" min="54" max="54"/>
+    <col width="29" customWidth="1" min="55" max="55"/>
     <col width="26" customWidth="1" min="56" max="56"/>
-    <col width="36" customWidth="1" min="57" max="57"/>
-    <col width="33" customWidth="1" min="58" max="58"/>
-    <col width="33" customWidth="1" min="59" max="59"/>
-    <col width="33" customWidth="1" min="60" max="60"/>
+    <col width="26" customWidth="1" min="57" max="57"/>
+    <col width="26" customWidth="1" min="58" max="58"/>
+    <col width="26" customWidth="1" min="59" max="59"/>
+    <col width="36" customWidth="1" min="60" max="60"/>
     <col width="33" customWidth="1" min="61" max="61"/>
-    <col width="40" customWidth="1" min="62" max="62"/>
-    <col width="37" customWidth="1" min="63" max="63"/>
-    <col width="37" customWidth="1" min="64" max="64"/>
-    <col width="37" customWidth="1" min="65" max="65"/>
+    <col width="33" customWidth="1" min="62" max="62"/>
+    <col width="33" customWidth="1" min="63" max="63"/>
+    <col width="33" customWidth="1" min="64" max="64"/>
+    <col width="40" customWidth="1" min="65" max="65"/>
     <col width="37" customWidth="1" min="66" max="66"/>
+    <col width="37" customWidth="1" min="67" max="67"/>
+    <col width="37" customWidth="1" min="68" max="68"/>
+    <col width="37" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -729,12 +732,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -779,7 +782,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Primary origin-event table contains 24 rows; registry keeps the frozen rooting-sensitivity count of 23. Primary ASR quality frame; 33 nonreference IQ-TREE composition-failed tips pruned.</t>
+          <t>Primary ASR quality frame; prunes the 33 nonreference IQ-TREE composition-failed tips.</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2025,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2052,12 +2055,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.5464098073555166</t>
+          <t>0.5456171735241503</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2156,17 +2159,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>561.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2186,12 +2189,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.5462478184991274</t>
+          <t>0.5436720142602496</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2243,17 +2246,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>561.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2293,7 +2296,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Original Reference/Tohama I rooted analysis retained as comparability sensitivity.</t>
+          <t>Original Reference/Tohama I rooted unpruned tree retained as comparability sensitivity.</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2367,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Fitch restricted to branches with support &gt;= 70 on the unpruned comparability frame</t>
+          <t>Unpruned comparability tree with Fitch origins restricted to branches with support &gt;=70.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2438,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Fitch restricted to branches with support &gt;= 90 on the unpruned comparability frame</t>
+          <t>Unpruned comparability tree with Fitch origins restricted to branches with support &gt;=90.</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2544,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2754,22 +2757,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.5462478184991274</t>
+          <t>0.5436720142602496</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5128,260 +5131,275 @@
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
+          <t>resampling_inference_scope</t>
+        </is>
+      </c>
+      <c r="P86" s="1" t="inlineStr">
+        <is>
+          <t>block_assignment_metadata_source</t>
+        </is>
+      </c>
+      <c r="Q86" s="1" t="inlineStr">
+        <is>
+          <t>block_assignment_inventory_source</t>
+        </is>
+      </c>
+      <c r="R86" s="1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="P86" s="1" t="inlineStr">
+      <c r="S86" s="1" t="inlineStr">
         <is>
           <t>n_replicates</t>
         </is>
       </c>
-      <c r="Q86" s="1" t="inlineStr">
+      <c r="T86" s="1" t="inlineStr">
         <is>
           <t>tip_count_median</t>
         </is>
       </c>
-      <c r="R86" s="1" t="inlineStr">
+      <c r="U86" s="1" t="inlineStr">
         <is>
           <t>tip_count_min</t>
         </is>
       </c>
-      <c r="S86" s="1" t="inlineStr">
+      <c r="V86" s="1" t="inlineStr">
         <is>
           <t>tip_count_max</t>
         </is>
       </c>
-      <c r="T86" s="1" t="inlineStr">
+      <c r="W86" s="1" t="inlineStr">
         <is>
           <t>tip_count_q25</t>
         </is>
       </c>
-      <c r="U86" s="1" t="inlineStr">
+      <c r="X86" s="1" t="inlineStr">
         <is>
           <t>tip_count_q75</t>
         </is>
       </c>
-      <c r="V86" s="1" t="inlineStr">
+      <c r="Y86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_median</t>
         </is>
       </c>
-      <c r="W86" s="1" t="inlineStr">
+      <c r="Z86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_min</t>
         </is>
       </c>
-      <c r="X86" s="1" t="inlineStr">
+      <c r="AA86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_max</t>
         </is>
       </c>
-      <c r="Y86" s="1" t="inlineStr">
+      <c r="AB86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_q25</t>
         </is>
       </c>
-      <c r="Z86" s="1" t="inlineStr">
+      <c r="AC86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_q75</t>
         </is>
       </c>
-      <c r="AA86" s="1" t="inlineStr">
+      <c r="AD86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_median</t>
         </is>
       </c>
-      <c r="AB86" s="1" t="inlineStr">
+      <c r="AE86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_min</t>
         </is>
       </c>
-      <c r="AC86" s="1" t="inlineStr">
+      <c r="AF86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_max</t>
         </is>
       </c>
-      <c r="AD86" s="1" t="inlineStr">
+      <c r="AG86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_q25</t>
         </is>
       </c>
-      <c r="AE86" s="1" t="inlineStr">
+      <c r="AH86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_q75</t>
         </is>
       </c>
-      <c r="AF86" s="1" t="inlineStr">
+      <c r="AI86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_median</t>
         </is>
       </c>
-      <c r="AG86" s="1" t="inlineStr">
+      <c r="AJ86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_min</t>
         </is>
       </c>
-      <c r="AH86" s="1" t="inlineStr">
+      <c r="AK86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_max</t>
         </is>
       </c>
-      <c r="AI86" s="1" t="inlineStr">
+      <c r="AL86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_q25</t>
         </is>
       </c>
-      <c r="AJ86" s="1" t="inlineStr">
+      <c r="AM86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_q75</t>
         </is>
       </c>
-      <c r="AK86" s="1" t="inlineStr">
+      <c r="AN86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_median</t>
         </is>
       </c>
-      <c r="AL86" s="1" t="inlineStr">
+      <c r="AO86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_min</t>
         </is>
       </c>
-      <c r="AM86" s="1" t="inlineStr">
+      <c r="AP86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_max</t>
         </is>
       </c>
-      <c r="AN86" s="1" t="inlineStr">
+      <c r="AQ86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_q25</t>
         </is>
       </c>
-      <c r="AO86" s="1" t="inlineStr">
+      <c r="AR86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_q75</t>
         </is>
       </c>
-      <c r="AP86" s="1" t="inlineStr">
+      <c r="AS86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_median</t>
         </is>
       </c>
-      <c r="AQ86" s="1" t="inlineStr">
+      <c r="AT86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_min</t>
         </is>
       </c>
-      <c r="AR86" s="1" t="inlineStr">
+      <c r="AU86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_max</t>
         </is>
       </c>
-      <c r="AS86" s="1" t="inlineStr">
+      <c r="AV86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_q25</t>
         </is>
       </c>
-      <c r="AT86" s="1" t="inlineStr">
+      <c r="AW86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_q75</t>
         </is>
       </c>
-      <c r="AU86" s="1" t="inlineStr">
+      <c r="AX86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_median</t>
         </is>
       </c>
-      <c r="AV86" s="1" t="inlineStr">
+      <c r="AY86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_min</t>
         </is>
       </c>
-      <c r="AW86" s="1" t="inlineStr">
+      <c r="AZ86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_max</t>
         </is>
       </c>
-      <c r="AX86" s="1" t="inlineStr">
+      <c r="BA86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_q25</t>
         </is>
       </c>
-      <c r="AY86" s="1" t="inlineStr">
+      <c r="BB86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_q75</t>
         </is>
       </c>
-      <c r="AZ86" s="1" t="inlineStr">
+      <c r="BC86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_median</t>
         </is>
       </c>
-      <c r="BA86" s="1" t="inlineStr">
+      <c r="BD86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_min</t>
         </is>
       </c>
-      <c r="BB86" s="1" t="inlineStr">
+      <c r="BE86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_max</t>
         </is>
       </c>
-      <c r="BC86" s="1" t="inlineStr">
+      <c r="BF86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_q25</t>
         </is>
       </c>
-      <c r="BD86" s="1" t="inlineStr">
+      <c r="BG86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_q75</t>
         </is>
       </c>
-      <c r="BE86" s="1" t="inlineStr">
+      <c r="BH86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_median</t>
         </is>
       </c>
-      <c r="BF86" s="1" t="inlineStr">
+      <c r="BI86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_min</t>
         </is>
       </c>
-      <c r="BG86" s="1" t="inlineStr">
+      <c r="BJ86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_max</t>
         </is>
       </c>
-      <c r="BH86" s="1" t="inlineStr">
+      <c r="BK86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_q25</t>
         </is>
       </c>
-      <c r="BI86" s="1" t="inlineStr">
+      <c r="BL86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_q75</t>
         </is>
       </c>
-      <c r="BJ86" s="1" t="inlineStr">
+      <c r="BM86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_median</t>
         </is>
       </c>
-      <c r="BK86" s="1" t="inlineStr">
+      <c r="BN86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_min</t>
         </is>
       </c>
-      <c r="BL86" s="1" t="inlineStr">
+      <c r="BO86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_max</t>
         </is>
       </c>
-      <c r="BM86" s="1" t="inlineStr">
+      <c r="BP86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_q25</t>
         </is>
       </c>
-      <c r="BN86" s="1" t="inlineStr">
+      <c r="BQ86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_q75</t>
         </is>
@@ -5425,12 +5443,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5460,12 +5478,24 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
@@ -5514,6 +5544,9 @@
       <c r="BL87" t="inlineStr"/>
       <c r="BM87" t="inlineStr"/>
       <c r="BN87" t="inlineStr"/>
+      <c r="BO87" t="inlineStr"/>
+      <c r="BP87" t="inlineStr"/>
+      <c r="BQ87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5553,12 +5586,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5588,12 +5621,24 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
@@ -5642,6 +5687,9 @@
       <c r="BL88" t="inlineStr"/>
       <c r="BM88" t="inlineStr"/>
       <c r="BN88" t="inlineStr"/>
+      <c r="BO88" t="inlineStr"/>
+      <c r="BP88" t="inlineStr"/>
+      <c r="BQ88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5681,12 +5729,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5716,12 +5764,24 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
@@ -5770,6 +5830,9 @@
       <c r="BL89" t="inlineStr"/>
       <c r="BM89" t="inlineStr"/>
       <c r="BN89" t="inlineStr"/>
+      <c r="BO89" t="inlineStr"/>
+      <c r="BP89" t="inlineStr"/>
+      <c r="BQ89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5809,12 +5872,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5844,12 +5907,24 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
@@ -5898,6 +5973,9 @@
       <c r="BL90" t="inlineStr"/>
       <c r="BM90" t="inlineStr"/>
       <c r="BN90" t="inlineStr"/>
+      <c r="BO90" t="inlineStr"/>
+      <c r="BP90" t="inlineStr"/>
+      <c r="BQ90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5937,12 +6015,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5972,12 +6050,24 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -6026,6 +6116,9 @@
       <c r="BL91" t="inlineStr"/>
       <c r="BM91" t="inlineStr"/>
       <c r="BN91" t="inlineStr"/>
+      <c r="BO91" t="inlineStr"/>
+      <c r="BP91" t="inlineStr"/>
+      <c r="BQ91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6065,12 +6158,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6100,12 +6193,24 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -6154,6 +6259,9 @@
       <c r="BL92" t="inlineStr"/>
       <c r="BM92" t="inlineStr"/>
       <c r="BN92" t="inlineStr"/>
+      <c r="BO92" t="inlineStr"/>
+      <c r="BP92" t="inlineStr"/>
+      <c r="BQ92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6193,12 +6301,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6228,12 +6336,24 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -6282,6 +6402,9 @@
       <c r="BL93" t="inlineStr"/>
       <c r="BM93" t="inlineStr"/>
       <c r="BN93" t="inlineStr"/>
+      <c r="BO93" t="inlineStr"/>
+      <c r="BP93" t="inlineStr"/>
+      <c r="BQ93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6321,12 +6444,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6356,12 +6479,24 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -6410,6 +6545,9 @@
       <c r="BL94" t="inlineStr"/>
       <c r="BM94" t="inlineStr"/>
       <c r="BN94" t="inlineStr"/>
+      <c r="BO94" t="inlineStr"/>
+      <c r="BP94" t="inlineStr"/>
+      <c r="BQ94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6449,12 +6587,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6484,12 +6622,24 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
@@ -6538,6 +6688,9 @@
       <c r="BL95" t="inlineStr"/>
       <c r="BM95" t="inlineStr"/>
       <c r="BN95" t="inlineStr"/>
+      <c r="BO95" t="inlineStr"/>
+      <c r="BP95" t="inlineStr"/>
+      <c r="BQ95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6577,12 +6730,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6612,12 +6765,24 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -6666,6 +6831,9 @@
       <c r="BL96" t="inlineStr"/>
       <c r="BM96" t="inlineStr"/>
       <c r="BN96" t="inlineStr"/>
+      <c r="BO96" t="inlineStr"/>
+      <c r="BP96" t="inlineStr"/>
+      <c r="BQ96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6696,260 +6864,275 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="U97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="V97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AD97" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AE97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
+      <c r="AF97" t="inlineStr">
         <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="AD97" t="inlineStr">
+      <c r="AG97" t="inlineStr">
         <is>
           <t>23.25</t>
         </is>
       </c>
-      <c r="AE97" t="inlineStr">
+      <c r="AH97" t="inlineStr">
         <is>
           <t>25.75</t>
         </is>
       </c>
-      <c r="AF97" t="inlineStr">
+      <c r="AI97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AG97" t="inlineStr">
+      <c r="AJ97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AH97" t="inlineStr">
+      <c r="AK97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AI97" t="inlineStr">
+      <c r="AL97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AJ97" t="inlineStr">
+      <c r="AM97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>1716.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>1716.0</t>
+          <t>1711.0</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1714.0</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1794.0</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1788.0</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
+          <t>1797.0</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>1792.25</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>1794.75</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AV97" t="inlineStr">
+      <c r="AY97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AW97" t="inlineStr">
+      <c r="AZ97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
+      <c r="BA97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AY97" t="inlineStr">
+      <c r="BB97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
+      <c r="BC97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BA97" t="inlineStr">
+      <c r="BD97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BB97" t="inlineStr">
+      <c r="BE97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BC97" t="inlineStr">
+      <c r="BF97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BD97" t="inlineStr">
+      <c r="BG97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BE97" t="inlineStr">
+      <c r="BH97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BF97" t="inlineStr">
+      <c r="BI97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BG97" t="inlineStr">
+      <c r="BJ97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BH97" t="inlineStr">
+      <c r="BK97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BI97" t="inlineStr">
+      <c r="BL97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BJ97" t="inlineStr">
+      <c r="BM97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BK97" t="inlineStr">
+      <c r="BN97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BL97" t="inlineStr">
+      <c r="BO97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BM97" t="inlineStr">
+      <c r="BP97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BN97" t="inlineStr">
+      <c r="BQ97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -6966,7 +7149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN97"/>
+  <dimension ref="A1:BQ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -6983,58 +7166,61 @@
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="37" customWidth="1" min="14" max="14"/>
-    <col width="62" customWidth="1" min="15" max="15"/>
-    <col width="31" customWidth="1" min="16" max="16"/>
+    <col width="57" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="62" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="62" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="25" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="27" customWidth="1" min="28" max="28"/>
-    <col width="27" customWidth="1" min="29" max="29"/>
-    <col width="27" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="25" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="30" max="30"/>
     <col width="27" customWidth="1" min="31" max="31"/>
-    <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
-    <col width="28" customWidth="1" min="34" max="34"/>
-    <col width="28" customWidth="1" min="35" max="35"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="27" customWidth="1" min="34" max="34"/>
+    <col width="31" customWidth="1" min="35" max="35"/>
     <col width="28" customWidth="1" min="36" max="36"/>
-    <col width="34" customWidth="1" min="37" max="37"/>
-    <col width="31" customWidth="1" min="38" max="38"/>
-    <col width="31" customWidth="1" min="39" max="39"/>
-    <col width="31" customWidth="1" min="40" max="40"/>
+    <col width="28" customWidth="1" min="37" max="37"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="39" max="39"/>
+    <col width="34" customWidth="1" min="40" max="40"/>
     <col width="31" customWidth="1" min="41" max="41"/>
     <col width="31" customWidth="1" min="42" max="42"/>
-    <col width="28" customWidth="1" min="43" max="43"/>
-    <col width="28" customWidth="1" min="44" max="44"/>
-    <col width="28" customWidth="1" min="45" max="45"/>
+    <col width="31" customWidth="1" min="43" max="43"/>
+    <col width="31" customWidth="1" min="44" max="44"/>
+    <col width="31" customWidth="1" min="45" max="45"/>
     <col width="28" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
-    <col width="25" customWidth="1" min="48" max="48"/>
-    <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="25" customWidth="1" min="50" max="50"/>
+    <col width="28" customWidth="1" min="48" max="48"/>
+    <col width="28" customWidth="1" min="49" max="49"/>
+    <col width="28" customWidth="1" min="50" max="50"/>
     <col width="25" customWidth="1" min="51" max="51"/>
-    <col width="29" customWidth="1" min="52" max="52"/>
-    <col width="26" customWidth="1" min="53" max="53"/>
-    <col width="26" customWidth="1" min="54" max="54"/>
-    <col width="26" customWidth="1" min="55" max="55"/>
+    <col width="25" customWidth="1" min="52" max="52"/>
+    <col width="25" customWidth="1" min="53" max="53"/>
+    <col width="25" customWidth="1" min="54" max="54"/>
+    <col width="29" customWidth="1" min="55" max="55"/>
     <col width="26" customWidth="1" min="56" max="56"/>
-    <col width="36" customWidth="1" min="57" max="57"/>
-    <col width="33" customWidth="1" min="58" max="58"/>
-    <col width="33" customWidth="1" min="59" max="59"/>
-    <col width="33" customWidth="1" min="60" max="60"/>
+    <col width="26" customWidth="1" min="57" max="57"/>
+    <col width="26" customWidth="1" min="58" max="58"/>
+    <col width="26" customWidth="1" min="59" max="59"/>
+    <col width="36" customWidth="1" min="60" max="60"/>
     <col width="33" customWidth="1" min="61" max="61"/>
-    <col width="40" customWidth="1" min="62" max="62"/>
-    <col width="37" customWidth="1" min="63" max="63"/>
-    <col width="37" customWidth="1" min="64" max="64"/>
-    <col width="37" customWidth="1" min="65" max="65"/>
+    <col width="33" customWidth="1" min="62" max="62"/>
+    <col width="33" customWidth="1" min="63" max="63"/>
+    <col width="33" customWidth="1" min="64" max="64"/>
+    <col width="40" customWidth="1" min="65" max="65"/>
     <col width="37" customWidth="1" min="66" max="66"/>
+    <col width="37" customWidth="1" min="67" max="67"/>
+    <col width="37" customWidth="1" min="68" max="68"/>
+    <col width="37" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7267,12 +7453,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -7317,7 +7503,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Primary origin-event table contains 24 rows; registry keeps the frozen rooting-sensitivity count of 23. Primary ASR quality frame; 33 nonreference IQ-TREE composition-failed tips pruned.</t>
+          <t>Primary ASR quality frame; prunes the 33 nonreference IQ-TREE composition-failed tips.</t>
         </is>
       </c>
     </row>
@@ -8560,12 +8746,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -8590,12 +8776,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.5464098073555166</t>
+          <t>0.5456171735241503</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -8694,17 +8880,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>561.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -8724,12 +8910,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.5462478184991274</t>
+          <t>0.5436720142602496</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -8781,17 +8967,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>561.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -8831,7 +9017,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Original Reference/Tohama I rooted analysis retained as comparability sensitivity.</t>
+          <t>Original Reference/Tohama I rooted unpruned tree retained as comparability sensitivity.</t>
         </is>
       </c>
     </row>
@@ -8902,7 +9088,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Fitch restricted to branches with support &gt;= 70 on the unpruned comparability frame</t>
+          <t>Unpruned comparability tree with Fitch origins restricted to branches with support &gt;=70.</t>
         </is>
       </c>
     </row>
@@ -8973,7 +9159,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Fitch restricted to branches with support &gt;= 90 on the unpruned comparability frame</t>
+          <t>Unpruned comparability tree with Fitch origins restricted to branches with support &gt;=90.</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9265,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -9292,22 +9478,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.5462478184991274</t>
+          <t>0.5436720142602496</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -11666,260 +11852,275 @@
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
+          <t>resampling_inference_scope</t>
+        </is>
+      </c>
+      <c r="P86" s="1" t="inlineStr">
+        <is>
+          <t>block_assignment_metadata_source</t>
+        </is>
+      </c>
+      <c r="Q86" s="1" t="inlineStr">
+        <is>
+          <t>block_assignment_inventory_source</t>
+        </is>
+      </c>
+      <c r="R86" s="1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="P86" s="1" t="inlineStr">
+      <c r="S86" s="1" t="inlineStr">
         <is>
           <t>n_replicates</t>
         </is>
       </c>
-      <c r="Q86" s="1" t="inlineStr">
+      <c r="T86" s="1" t="inlineStr">
         <is>
           <t>tip_count_median</t>
         </is>
       </c>
-      <c r="R86" s="1" t="inlineStr">
+      <c r="U86" s="1" t="inlineStr">
         <is>
           <t>tip_count_min</t>
         </is>
       </c>
-      <c r="S86" s="1" t="inlineStr">
+      <c r="V86" s="1" t="inlineStr">
         <is>
           <t>tip_count_max</t>
         </is>
       </c>
-      <c r="T86" s="1" t="inlineStr">
+      <c r="W86" s="1" t="inlineStr">
         <is>
           <t>tip_count_q25</t>
         </is>
       </c>
-      <c r="U86" s="1" t="inlineStr">
+      <c r="X86" s="1" t="inlineStr">
         <is>
           <t>tip_count_q75</t>
         </is>
       </c>
-      <c r="V86" s="1" t="inlineStr">
+      <c r="Y86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_median</t>
         </is>
       </c>
-      <c r="W86" s="1" t="inlineStr">
+      <c r="Z86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_min</t>
         </is>
       </c>
-      <c r="X86" s="1" t="inlineStr">
+      <c r="AA86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_max</t>
         </is>
       </c>
-      <c r="Y86" s="1" t="inlineStr">
+      <c r="AB86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_q25</t>
         </is>
       </c>
-      <c r="Z86" s="1" t="inlineStr">
+      <c r="AC86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_q75</t>
         </is>
       </c>
-      <c r="AA86" s="1" t="inlineStr">
+      <c r="AD86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_median</t>
         </is>
       </c>
-      <c r="AB86" s="1" t="inlineStr">
+      <c r="AE86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_min</t>
         </is>
       </c>
-      <c r="AC86" s="1" t="inlineStr">
+      <c r="AF86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_max</t>
         </is>
       </c>
-      <c r="AD86" s="1" t="inlineStr">
+      <c r="AG86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_q25</t>
         </is>
       </c>
-      <c r="AE86" s="1" t="inlineStr">
+      <c r="AH86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_q75</t>
         </is>
       </c>
-      <c r="AF86" s="1" t="inlineStr">
+      <c r="AI86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_median</t>
         </is>
       </c>
-      <c r="AG86" s="1" t="inlineStr">
+      <c r="AJ86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_min</t>
         </is>
       </c>
-      <c r="AH86" s="1" t="inlineStr">
+      <c r="AK86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_max</t>
         </is>
       </c>
-      <c r="AI86" s="1" t="inlineStr">
+      <c r="AL86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_q25</t>
         </is>
       </c>
-      <c r="AJ86" s="1" t="inlineStr">
+      <c r="AM86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_q75</t>
         </is>
       </c>
-      <c r="AK86" s="1" t="inlineStr">
+      <c r="AN86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_median</t>
         </is>
       </c>
-      <c r="AL86" s="1" t="inlineStr">
+      <c r="AO86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_min</t>
         </is>
       </c>
-      <c r="AM86" s="1" t="inlineStr">
+      <c r="AP86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_max</t>
         </is>
       </c>
-      <c r="AN86" s="1" t="inlineStr">
+      <c r="AQ86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_q25</t>
         </is>
       </c>
-      <c r="AO86" s="1" t="inlineStr">
+      <c r="AR86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_q75</t>
         </is>
       </c>
-      <c r="AP86" s="1" t="inlineStr">
+      <c r="AS86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_median</t>
         </is>
       </c>
-      <c r="AQ86" s="1" t="inlineStr">
+      <c r="AT86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_min</t>
         </is>
       </c>
-      <c r="AR86" s="1" t="inlineStr">
+      <c r="AU86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_max</t>
         </is>
       </c>
-      <c r="AS86" s="1" t="inlineStr">
+      <c r="AV86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_q25</t>
         </is>
       </c>
-      <c r="AT86" s="1" t="inlineStr">
+      <c r="AW86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_q75</t>
         </is>
       </c>
-      <c r="AU86" s="1" t="inlineStr">
+      <c r="AX86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_median</t>
         </is>
       </c>
-      <c r="AV86" s="1" t="inlineStr">
+      <c r="AY86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_min</t>
         </is>
       </c>
-      <c r="AW86" s="1" t="inlineStr">
+      <c r="AZ86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_max</t>
         </is>
       </c>
-      <c r="AX86" s="1" t="inlineStr">
+      <c r="BA86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_q25</t>
         </is>
       </c>
-      <c r="AY86" s="1" t="inlineStr">
+      <c r="BB86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_q75</t>
         </is>
       </c>
-      <c r="AZ86" s="1" t="inlineStr">
+      <c r="BC86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_median</t>
         </is>
       </c>
-      <c r="BA86" s="1" t="inlineStr">
+      <c r="BD86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_min</t>
         </is>
       </c>
-      <c r="BB86" s="1" t="inlineStr">
+      <c r="BE86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_max</t>
         </is>
       </c>
-      <c r="BC86" s="1" t="inlineStr">
+      <c r="BF86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_q25</t>
         </is>
       </c>
-      <c r="BD86" s="1" t="inlineStr">
+      <c r="BG86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_q75</t>
         </is>
       </c>
-      <c r="BE86" s="1" t="inlineStr">
+      <c r="BH86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_median</t>
         </is>
       </c>
-      <c r="BF86" s="1" t="inlineStr">
+      <c r="BI86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_min</t>
         </is>
       </c>
-      <c r="BG86" s="1" t="inlineStr">
+      <c r="BJ86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_max</t>
         </is>
       </c>
-      <c r="BH86" s="1" t="inlineStr">
+      <c r="BK86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_q25</t>
         </is>
       </c>
-      <c r="BI86" s="1" t="inlineStr">
+      <c r="BL86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_q75</t>
         </is>
       </c>
-      <c r="BJ86" s="1" t="inlineStr">
+      <c r="BM86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_median</t>
         </is>
       </c>
-      <c r="BK86" s="1" t="inlineStr">
+      <c r="BN86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_min</t>
         </is>
       </c>
-      <c r="BL86" s="1" t="inlineStr">
+      <c r="BO86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_max</t>
         </is>
       </c>
-      <c r="BM86" s="1" t="inlineStr">
+      <c r="BP86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_q25</t>
         </is>
       </c>
-      <c r="BN86" s="1" t="inlineStr">
+      <c r="BQ86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_q75</t>
         </is>
@@ -11963,12 +12164,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11998,12 +12199,24 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
@@ -12052,6 +12265,9 @@
       <c r="BL87" t="inlineStr"/>
       <c r="BM87" t="inlineStr"/>
       <c r="BN87" t="inlineStr"/>
+      <c r="BO87" t="inlineStr"/>
+      <c r="BP87" t="inlineStr"/>
+      <c r="BQ87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -12091,12 +12307,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -12126,12 +12342,24 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
@@ -12180,6 +12408,9 @@
       <c r="BL88" t="inlineStr"/>
       <c r="BM88" t="inlineStr"/>
       <c r="BN88" t="inlineStr"/>
+      <c r="BO88" t="inlineStr"/>
+      <c r="BP88" t="inlineStr"/>
+      <c r="BQ88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -12219,12 +12450,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -12254,12 +12485,24 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
@@ -12308,6 +12551,9 @@
       <c r="BL89" t="inlineStr"/>
       <c r="BM89" t="inlineStr"/>
       <c r="BN89" t="inlineStr"/>
+      <c r="BO89" t="inlineStr"/>
+      <c r="BP89" t="inlineStr"/>
+      <c r="BQ89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -12347,12 +12593,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -12382,12 +12628,24 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
@@ -12436,6 +12694,9 @@
       <c r="BL90" t="inlineStr"/>
       <c r="BM90" t="inlineStr"/>
       <c r="BN90" t="inlineStr"/>
+      <c r="BO90" t="inlineStr"/>
+      <c r="BP90" t="inlineStr"/>
+      <c r="BQ90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -12475,12 +12736,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -12510,12 +12771,24 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -12564,6 +12837,9 @@
       <c r="BL91" t="inlineStr"/>
       <c r="BM91" t="inlineStr"/>
       <c r="BN91" t="inlineStr"/>
+      <c r="BO91" t="inlineStr"/>
+      <c r="BP91" t="inlineStr"/>
+      <c r="BQ91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -12603,12 +12879,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -12638,12 +12914,24 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -12692,6 +12980,9 @@
       <c r="BL92" t="inlineStr"/>
       <c r="BM92" t="inlineStr"/>
       <c r="BN92" t="inlineStr"/>
+      <c r="BO92" t="inlineStr"/>
+      <c r="BP92" t="inlineStr"/>
+      <c r="BQ92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -12731,12 +13022,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -12766,12 +13057,24 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -12820,6 +13123,9 @@
       <c r="BL93" t="inlineStr"/>
       <c r="BM93" t="inlineStr"/>
       <c r="BN93" t="inlineStr"/>
+      <c r="BO93" t="inlineStr"/>
+      <c r="BP93" t="inlineStr"/>
+      <c r="BQ93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -12859,12 +13165,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -12894,12 +13200,24 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -12948,6 +13266,9 @@
       <c r="BL94" t="inlineStr"/>
       <c r="BM94" t="inlineStr"/>
       <c r="BN94" t="inlineStr"/>
+      <c r="BO94" t="inlineStr"/>
+      <c r="BP94" t="inlineStr"/>
+      <c r="BQ94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12987,12 +13308,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -13022,12 +13343,24 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
@@ -13076,6 +13409,9 @@
       <c r="BL95" t="inlineStr"/>
       <c r="BM95" t="inlineStr"/>
       <c r="BN95" t="inlineStr"/>
+      <c r="BO95" t="inlineStr"/>
+      <c r="BP95" t="inlineStr"/>
+      <c r="BQ95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -13115,12 +13451,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -13150,12 +13486,24 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -13204,6 +13552,9 @@
       <c r="BL96" t="inlineStr"/>
       <c r="BM96" t="inlineStr"/>
       <c r="BN96" t="inlineStr"/>
+      <c r="BO96" t="inlineStr"/>
+      <c r="BP96" t="inlineStr"/>
+      <c r="BQ96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -13234,260 +13585,275 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="U97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="V97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AD97" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AE97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
+      <c r="AF97" t="inlineStr">
         <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="AD97" t="inlineStr">
+      <c r="AG97" t="inlineStr">
         <is>
           <t>23.25</t>
         </is>
       </c>
-      <c r="AE97" t="inlineStr">
+      <c r="AH97" t="inlineStr">
         <is>
           <t>25.75</t>
         </is>
       </c>
-      <c r="AF97" t="inlineStr">
+      <c r="AI97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AG97" t="inlineStr">
+      <c r="AJ97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AH97" t="inlineStr">
+      <c r="AK97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AI97" t="inlineStr">
+      <c r="AL97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AJ97" t="inlineStr">
+      <c r="AM97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>1716.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>1716.0</t>
+          <t>1711.0</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1714.0</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1794.0</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1788.0</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
+          <t>1797.0</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>1792.25</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>1794.75</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AV97" t="inlineStr">
+      <c r="AY97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AW97" t="inlineStr">
+      <c r="AZ97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
+      <c r="BA97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AY97" t="inlineStr">
+      <c r="BB97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
+      <c r="BC97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BA97" t="inlineStr">
+      <c r="BD97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BB97" t="inlineStr">
+      <c r="BE97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BC97" t="inlineStr">
+      <c r="BF97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BD97" t="inlineStr">
+      <c r="BG97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BE97" t="inlineStr">
+      <c r="BH97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BF97" t="inlineStr">
+      <c r="BI97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BG97" t="inlineStr">
+      <c r="BJ97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BH97" t="inlineStr">
+      <c r="BK97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BI97" t="inlineStr">
+      <c r="BL97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BJ97" t="inlineStr">
+      <c r="BM97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BK97" t="inlineStr">
+      <c r="BN97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BL97" t="inlineStr">
+      <c r="BO97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BM97" t="inlineStr">
+      <c r="BP97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BN97" t="inlineStr">
+      <c r="BQ97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -13504,7 +13870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN97"/>
+  <dimension ref="A1:BQ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -13521,58 +13887,61 @@
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="37" customWidth="1" min="14" max="14"/>
-    <col width="62" customWidth="1" min="15" max="15"/>
-    <col width="31" customWidth="1" min="16" max="16"/>
+    <col width="57" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="62" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="62" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="25" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="27" customWidth="1" min="28" max="28"/>
-    <col width="27" customWidth="1" min="29" max="29"/>
-    <col width="27" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="25" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="30" max="30"/>
     <col width="27" customWidth="1" min="31" max="31"/>
-    <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
-    <col width="28" customWidth="1" min="34" max="34"/>
-    <col width="28" customWidth="1" min="35" max="35"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="27" customWidth="1" min="34" max="34"/>
+    <col width="31" customWidth="1" min="35" max="35"/>
     <col width="28" customWidth="1" min="36" max="36"/>
-    <col width="34" customWidth="1" min="37" max="37"/>
-    <col width="31" customWidth="1" min="38" max="38"/>
-    <col width="31" customWidth="1" min="39" max="39"/>
-    <col width="31" customWidth="1" min="40" max="40"/>
+    <col width="28" customWidth="1" min="37" max="37"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="39" max="39"/>
+    <col width="34" customWidth="1" min="40" max="40"/>
     <col width="31" customWidth="1" min="41" max="41"/>
     <col width="31" customWidth="1" min="42" max="42"/>
-    <col width="28" customWidth="1" min="43" max="43"/>
-    <col width="28" customWidth="1" min="44" max="44"/>
-    <col width="28" customWidth="1" min="45" max="45"/>
+    <col width="31" customWidth="1" min="43" max="43"/>
+    <col width="31" customWidth="1" min="44" max="44"/>
+    <col width="31" customWidth="1" min="45" max="45"/>
     <col width="28" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
-    <col width="25" customWidth="1" min="48" max="48"/>
-    <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="25" customWidth="1" min="50" max="50"/>
+    <col width="28" customWidth="1" min="48" max="48"/>
+    <col width="28" customWidth="1" min="49" max="49"/>
+    <col width="28" customWidth="1" min="50" max="50"/>
     <col width="25" customWidth="1" min="51" max="51"/>
-    <col width="29" customWidth="1" min="52" max="52"/>
-    <col width="26" customWidth="1" min="53" max="53"/>
-    <col width="26" customWidth="1" min="54" max="54"/>
-    <col width="26" customWidth="1" min="55" max="55"/>
+    <col width="25" customWidth="1" min="52" max="52"/>
+    <col width="25" customWidth="1" min="53" max="53"/>
+    <col width="25" customWidth="1" min="54" max="54"/>
+    <col width="29" customWidth="1" min="55" max="55"/>
     <col width="26" customWidth="1" min="56" max="56"/>
-    <col width="36" customWidth="1" min="57" max="57"/>
-    <col width="33" customWidth="1" min="58" max="58"/>
-    <col width="33" customWidth="1" min="59" max="59"/>
-    <col width="33" customWidth="1" min="60" max="60"/>
+    <col width="26" customWidth="1" min="57" max="57"/>
+    <col width="26" customWidth="1" min="58" max="58"/>
+    <col width="26" customWidth="1" min="59" max="59"/>
+    <col width="36" customWidth="1" min="60" max="60"/>
     <col width="33" customWidth="1" min="61" max="61"/>
-    <col width="40" customWidth="1" min="62" max="62"/>
-    <col width="37" customWidth="1" min="63" max="63"/>
-    <col width="37" customWidth="1" min="64" max="64"/>
-    <col width="37" customWidth="1" min="65" max="65"/>
+    <col width="33" customWidth="1" min="62" max="62"/>
+    <col width="33" customWidth="1" min="63" max="63"/>
+    <col width="33" customWidth="1" min="64" max="64"/>
+    <col width="40" customWidth="1" min="65" max="65"/>
     <col width="37" customWidth="1" min="66" max="66"/>
+    <col width="37" customWidth="1" min="67" max="67"/>
+    <col width="37" customWidth="1" min="68" max="68"/>
+    <col width="37" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13805,12 +14174,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -13855,7 +14224,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Primary origin-event table contains 24 rows; registry keeps the frozen rooting-sensitivity count of 23. Primary ASR quality frame; 33 nonreference IQ-TREE composition-failed tips pruned.</t>
+          <t>Primary ASR quality frame; prunes the 33 nonreference IQ-TREE composition-failed tips.</t>
         </is>
       </c>
     </row>
@@ -15098,12 +15467,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -15128,12 +15497,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.5464098073555166</t>
+          <t>0.5456171735241503</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -15232,17 +15601,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>561.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -15262,12 +15631,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.5462478184991274</t>
+          <t>0.5436720142602496</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -15319,17 +15688,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>561.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -15369,7 +15738,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Original Reference/Tohama I rooted analysis retained as comparability sensitivity.</t>
+          <t>Original Reference/Tohama I rooted unpruned tree retained as comparability sensitivity.</t>
         </is>
       </c>
     </row>
@@ -15440,7 +15809,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Fitch restricted to branches with support &gt;= 70 on the unpruned comparability frame</t>
+          <t>Unpruned comparability tree with Fitch origins restricted to branches with support &gt;=70.</t>
         </is>
       </c>
     </row>
@@ -15511,7 +15880,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Fitch restricted to branches with support &gt;= 90 on the unpruned comparability frame</t>
+          <t>Unpruned comparability tree with Fitch origins restricted to branches with support &gt;=90.</t>
         </is>
       </c>
     </row>
@@ -15617,7 +15986,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -15830,22 +16199,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.5462478184991274</t>
+          <t>0.5436720142602496</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -18204,260 +18573,275 @@
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
+          <t>resampling_inference_scope</t>
+        </is>
+      </c>
+      <c r="P86" s="1" t="inlineStr">
+        <is>
+          <t>block_assignment_metadata_source</t>
+        </is>
+      </c>
+      <c r="Q86" s="1" t="inlineStr">
+        <is>
+          <t>block_assignment_inventory_source</t>
+        </is>
+      </c>
+      <c r="R86" s="1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="P86" s="1" t="inlineStr">
+      <c r="S86" s="1" t="inlineStr">
         <is>
           <t>n_replicates</t>
         </is>
       </c>
-      <c r="Q86" s="1" t="inlineStr">
+      <c r="T86" s="1" t="inlineStr">
         <is>
           <t>tip_count_median</t>
         </is>
       </c>
-      <c r="R86" s="1" t="inlineStr">
+      <c r="U86" s="1" t="inlineStr">
         <is>
           <t>tip_count_min</t>
         </is>
       </c>
-      <c r="S86" s="1" t="inlineStr">
+      <c r="V86" s="1" t="inlineStr">
         <is>
           <t>tip_count_max</t>
         </is>
       </c>
-      <c r="T86" s="1" t="inlineStr">
+      <c r="W86" s="1" t="inlineStr">
         <is>
           <t>tip_count_q25</t>
         </is>
       </c>
-      <c r="U86" s="1" t="inlineStr">
+      <c r="X86" s="1" t="inlineStr">
         <is>
           <t>tip_count_q75</t>
         </is>
       </c>
-      <c r="V86" s="1" t="inlineStr">
+      <c r="Y86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_median</t>
         </is>
       </c>
-      <c r="W86" s="1" t="inlineStr">
+      <c r="Z86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_min</t>
         </is>
       </c>
-      <c r="X86" s="1" t="inlineStr">
+      <c r="AA86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_max</t>
         </is>
       </c>
-      <c r="Y86" s="1" t="inlineStr">
+      <c r="AB86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_q25</t>
         </is>
       </c>
-      <c r="Z86" s="1" t="inlineStr">
+      <c r="AC86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_q75</t>
         </is>
       </c>
-      <c r="AA86" s="1" t="inlineStr">
+      <c r="AD86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_median</t>
         </is>
       </c>
-      <c r="AB86" s="1" t="inlineStr">
+      <c r="AE86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_min</t>
         </is>
       </c>
-      <c r="AC86" s="1" t="inlineStr">
+      <c r="AF86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_max</t>
         </is>
       </c>
-      <c r="AD86" s="1" t="inlineStr">
+      <c r="AG86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_q25</t>
         </is>
       </c>
-      <c r="AE86" s="1" t="inlineStr">
+      <c r="AH86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_q75</t>
         </is>
       </c>
-      <c r="AF86" s="1" t="inlineStr">
+      <c r="AI86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_median</t>
         </is>
       </c>
-      <c r="AG86" s="1" t="inlineStr">
+      <c r="AJ86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_min</t>
         </is>
       </c>
-      <c r="AH86" s="1" t="inlineStr">
+      <c r="AK86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_max</t>
         </is>
       </c>
-      <c r="AI86" s="1" t="inlineStr">
+      <c r="AL86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_q25</t>
         </is>
       </c>
-      <c r="AJ86" s="1" t="inlineStr">
+      <c r="AM86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_q75</t>
         </is>
       </c>
-      <c r="AK86" s="1" t="inlineStr">
+      <c r="AN86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_median</t>
         </is>
       </c>
-      <c r="AL86" s="1" t="inlineStr">
+      <c r="AO86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_min</t>
         </is>
       </c>
-      <c r="AM86" s="1" t="inlineStr">
+      <c r="AP86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_max</t>
         </is>
       </c>
-      <c r="AN86" s="1" t="inlineStr">
+      <c r="AQ86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_q25</t>
         </is>
       </c>
-      <c r="AO86" s="1" t="inlineStr">
+      <c r="AR86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_q75</t>
         </is>
       </c>
-      <c r="AP86" s="1" t="inlineStr">
+      <c r="AS86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_median</t>
         </is>
       </c>
-      <c r="AQ86" s="1" t="inlineStr">
+      <c r="AT86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_min</t>
         </is>
       </c>
-      <c r="AR86" s="1" t="inlineStr">
+      <c r="AU86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_max</t>
         </is>
       </c>
-      <c r="AS86" s="1" t="inlineStr">
+      <c r="AV86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_q25</t>
         </is>
       </c>
-      <c r="AT86" s="1" t="inlineStr">
+      <c r="AW86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_q75</t>
         </is>
       </c>
-      <c r="AU86" s="1" t="inlineStr">
+      <c r="AX86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_median</t>
         </is>
       </c>
-      <c r="AV86" s="1" t="inlineStr">
+      <c r="AY86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_min</t>
         </is>
       </c>
-      <c r="AW86" s="1" t="inlineStr">
+      <c r="AZ86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_max</t>
         </is>
       </c>
-      <c r="AX86" s="1" t="inlineStr">
+      <c r="BA86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_q25</t>
         </is>
       </c>
-      <c r="AY86" s="1" t="inlineStr">
+      <c r="BB86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_q75</t>
         </is>
       </c>
-      <c r="AZ86" s="1" t="inlineStr">
+      <c r="BC86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_median</t>
         </is>
       </c>
-      <c r="BA86" s="1" t="inlineStr">
+      <c r="BD86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_min</t>
         </is>
       </c>
-      <c r="BB86" s="1" t="inlineStr">
+      <c r="BE86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_max</t>
         </is>
       </c>
-      <c r="BC86" s="1" t="inlineStr">
+      <c r="BF86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_q25</t>
         </is>
       </c>
-      <c r="BD86" s="1" t="inlineStr">
+      <c r="BG86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_q75</t>
         </is>
       </c>
-      <c r="BE86" s="1" t="inlineStr">
+      <c r="BH86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_median</t>
         </is>
       </c>
-      <c r="BF86" s="1" t="inlineStr">
+      <c r="BI86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_min</t>
         </is>
       </c>
-      <c r="BG86" s="1" t="inlineStr">
+      <c r="BJ86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_max</t>
         </is>
       </c>
-      <c r="BH86" s="1" t="inlineStr">
+      <c r="BK86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_q25</t>
         </is>
       </c>
-      <c r="BI86" s="1" t="inlineStr">
+      <c r="BL86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_q75</t>
         </is>
       </c>
-      <c r="BJ86" s="1" t="inlineStr">
+      <c r="BM86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_median</t>
         </is>
       </c>
-      <c r="BK86" s="1" t="inlineStr">
+      <c r="BN86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_min</t>
         </is>
       </c>
-      <c r="BL86" s="1" t="inlineStr">
+      <c r="BO86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_max</t>
         </is>
       </c>
-      <c r="BM86" s="1" t="inlineStr">
+      <c r="BP86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_q25</t>
         </is>
       </c>
-      <c r="BN86" s="1" t="inlineStr">
+      <c r="BQ86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_q75</t>
         </is>
@@ -18501,12 +18885,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -18536,12 +18920,24 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
@@ -18590,6 +18986,9 @@
       <c r="BL87" t="inlineStr"/>
       <c r="BM87" t="inlineStr"/>
       <c r="BN87" t="inlineStr"/>
+      <c r="BO87" t="inlineStr"/>
+      <c r="BP87" t="inlineStr"/>
+      <c r="BQ87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -18629,12 +19028,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -18664,12 +19063,24 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
@@ -18718,6 +19129,9 @@
       <c r="BL88" t="inlineStr"/>
       <c r="BM88" t="inlineStr"/>
       <c r="BN88" t="inlineStr"/>
+      <c r="BO88" t="inlineStr"/>
+      <c r="BP88" t="inlineStr"/>
+      <c r="BQ88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -18757,12 +19171,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -18792,12 +19206,24 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
@@ -18846,6 +19272,9 @@
       <c r="BL89" t="inlineStr"/>
       <c r="BM89" t="inlineStr"/>
       <c r="BN89" t="inlineStr"/>
+      <c r="BO89" t="inlineStr"/>
+      <c r="BP89" t="inlineStr"/>
+      <c r="BQ89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18885,12 +19314,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -18920,12 +19349,24 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
@@ -18974,6 +19415,9 @@
       <c r="BL90" t="inlineStr"/>
       <c r="BM90" t="inlineStr"/>
       <c r="BN90" t="inlineStr"/>
+      <c r="BO90" t="inlineStr"/>
+      <c r="BP90" t="inlineStr"/>
+      <c r="BQ90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19013,12 +19457,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -19048,12 +19492,24 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -19102,6 +19558,9 @@
       <c r="BL91" t="inlineStr"/>
       <c r="BM91" t="inlineStr"/>
       <c r="BN91" t="inlineStr"/>
+      <c r="BO91" t="inlineStr"/>
+      <c r="BP91" t="inlineStr"/>
+      <c r="BQ91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -19141,12 +19600,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -19176,12 +19635,24 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -19230,6 +19701,9 @@
       <c r="BL92" t="inlineStr"/>
       <c r="BM92" t="inlineStr"/>
       <c r="BN92" t="inlineStr"/>
+      <c r="BO92" t="inlineStr"/>
+      <c r="BP92" t="inlineStr"/>
+      <c r="BQ92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19269,12 +19743,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -19304,12 +19778,24 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -19358,6 +19844,9 @@
       <c r="BL93" t="inlineStr"/>
       <c r="BM93" t="inlineStr"/>
       <c r="BN93" t="inlineStr"/>
+      <c r="BO93" t="inlineStr"/>
+      <c r="BP93" t="inlineStr"/>
+      <c r="BQ93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19397,12 +19886,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -19432,12 +19921,24 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -19486,6 +19987,9 @@
       <c r="BL94" t="inlineStr"/>
       <c r="BM94" t="inlineStr"/>
       <c r="BN94" t="inlineStr"/>
+      <c r="BO94" t="inlineStr"/>
+      <c r="BP94" t="inlineStr"/>
+      <c r="BQ94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19525,12 +20029,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -19560,12 +20064,24 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
@@ -19614,6 +20130,9 @@
       <c r="BL95" t="inlineStr"/>
       <c r="BM95" t="inlineStr"/>
       <c r="BN95" t="inlineStr"/>
+      <c r="BO95" t="inlineStr"/>
+      <c r="BP95" t="inlineStr"/>
+      <c r="BQ95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19653,12 +20172,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -19688,12 +20207,24 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -19742,6 +20273,9 @@
       <c r="BL96" t="inlineStr"/>
       <c r="BM96" t="inlineStr"/>
       <c r="BN96" t="inlineStr"/>
+      <c r="BO96" t="inlineStr"/>
+      <c r="BP96" t="inlineStr"/>
+      <c r="BQ96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19772,260 +20306,275 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="U97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="V97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AD97" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AE97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
+      <c r="AF97" t="inlineStr">
         <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="AD97" t="inlineStr">
+      <c r="AG97" t="inlineStr">
         <is>
           <t>23.25</t>
         </is>
       </c>
-      <c r="AE97" t="inlineStr">
+      <c r="AH97" t="inlineStr">
         <is>
           <t>25.75</t>
         </is>
       </c>
-      <c r="AF97" t="inlineStr">
+      <c r="AI97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AG97" t="inlineStr">
+      <c r="AJ97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AH97" t="inlineStr">
+      <c r="AK97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AI97" t="inlineStr">
+      <c r="AL97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AJ97" t="inlineStr">
+      <c r="AM97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>1716.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>1716.0</t>
+          <t>1711.0</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1714.0</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1794.0</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1788.0</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
+          <t>1797.0</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>1792.25</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>1794.75</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AV97" t="inlineStr">
+      <c r="AY97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AW97" t="inlineStr">
+      <c r="AZ97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
+      <c r="BA97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AY97" t="inlineStr">
+      <c r="BB97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
+      <c r="BC97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BA97" t="inlineStr">
+      <c r="BD97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BB97" t="inlineStr">
+      <c r="BE97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BC97" t="inlineStr">
+      <c r="BF97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BD97" t="inlineStr">
+      <c r="BG97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BE97" t="inlineStr">
+      <c r="BH97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BF97" t="inlineStr">
+      <c r="BI97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BG97" t="inlineStr">
+      <c r="BJ97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BH97" t="inlineStr">
+      <c r="BK97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BI97" t="inlineStr">
+      <c r="BL97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BJ97" t="inlineStr">
+      <c r="BM97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BK97" t="inlineStr">
+      <c r="BN97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BL97" t="inlineStr">
+      <c r="BO97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BM97" t="inlineStr">
+      <c r="BP97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BN97" t="inlineStr">
+      <c r="BQ97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -20042,7 +20591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN97"/>
+  <dimension ref="A1:BQ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -20059,58 +20608,61 @@
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="37" customWidth="1" min="14" max="14"/>
-    <col width="62" customWidth="1" min="15" max="15"/>
-    <col width="31" customWidth="1" min="16" max="16"/>
+    <col width="57" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="62" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="62" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="25" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="27" customWidth="1" min="28" max="28"/>
-    <col width="27" customWidth="1" min="29" max="29"/>
-    <col width="27" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="25" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="30" max="30"/>
     <col width="27" customWidth="1" min="31" max="31"/>
-    <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
-    <col width="28" customWidth="1" min="34" max="34"/>
-    <col width="28" customWidth="1" min="35" max="35"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="27" customWidth="1" min="34" max="34"/>
+    <col width="31" customWidth="1" min="35" max="35"/>
     <col width="28" customWidth="1" min="36" max="36"/>
-    <col width="34" customWidth="1" min="37" max="37"/>
-    <col width="31" customWidth="1" min="38" max="38"/>
-    <col width="31" customWidth="1" min="39" max="39"/>
-    <col width="31" customWidth="1" min="40" max="40"/>
+    <col width="28" customWidth="1" min="37" max="37"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="39" max="39"/>
+    <col width="34" customWidth="1" min="40" max="40"/>
     <col width="31" customWidth="1" min="41" max="41"/>
     <col width="31" customWidth="1" min="42" max="42"/>
-    <col width="28" customWidth="1" min="43" max="43"/>
-    <col width="28" customWidth="1" min="44" max="44"/>
-    <col width="28" customWidth="1" min="45" max="45"/>
+    <col width="31" customWidth="1" min="43" max="43"/>
+    <col width="31" customWidth="1" min="44" max="44"/>
+    <col width="31" customWidth="1" min="45" max="45"/>
     <col width="28" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
-    <col width="25" customWidth="1" min="48" max="48"/>
-    <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="25" customWidth="1" min="50" max="50"/>
+    <col width="28" customWidth="1" min="48" max="48"/>
+    <col width="28" customWidth="1" min="49" max="49"/>
+    <col width="28" customWidth="1" min="50" max="50"/>
     <col width="25" customWidth="1" min="51" max="51"/>
-    <col width="29" customWidth="1" min="52" max="52"/>
-    <col width="26" customWidth="1" min="53" max="53"/>
-    <col width="26" customWidth="1" min="54" max="54"/>
-    <col width="26" customWidth="1" min="55" max="55"/>
+    <col width="25" customWidth="1" min="52" max="52"/>
+    <col width="25" customWidth="1" min="53" max="53"/>
+    <col width="25" customWidth="1" min="54" max="54"/>
+    <col width="29" customWidth="1" min="55" max="55"/>
     <col width="26" customWidth="1" min="56" max="56"/>
-    <col width="36" customWidth="1" min="57" max="57"/>
-    <col width="33" customWidth="1" min="58" max="58"/>
-    <col width="33" customWidth="1" min="59" max="59"/>
-    <col width="33" customWidth="1" min="60" max="60"/>
+    <col width="26" customWidth="1" min="57" max="57"/>
+    <col width="26" customWidth="1" min="58" max="58"/>
+    <col width="26" customWidth="1" min="59" max="59"/>
+    <col width="36" customWidth="1" min="60" max="60"/>
     <col width="33" customWidth="1" min="61" max="61"/>
-    <col width="40" customWidth="1" min="62" max="62"/>
-    <col width="37" customWidth="1" min="63" max="63"/>
-    <col width="37" customWidth="1" min="64" max="64"/>
-    <col width="37" customWidth="1" min="65" max="65"/>
+    <col width="33" customWidth="1" min="62" max="62"/>
+    <col width="33" customWidth="1" min="63" max="63"/>
+    <col width="33" customWidth="1" min="64" max="64"/>
+    <col width="40" customWidth="1" min="65" max="65"/>
     <col width="37" customWidth="1" min="66" max="66"/>
+    <col width="37" customWidth="1" min="67" max="67"/>
+    <col width="37" customWidth="1" min="68" max="68"/>
+    <col width="37" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20343,12 +20895,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -20393,7 +20945,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Primary origin-event table contains 24 rows; registry keeps the frozen rooting-sensitivity count of 23. Primary ASR quality frame; 33 nonreference IQ-TREE composition-failed tips pruned.</t>
+          <t>Primary ASR quality frame; prunes the 33 nonreference IQ-TREE composition-failed tips.</t>
         </is>
       </c>
     </row>
@@ -21636,12 +22188,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>559.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -21666,12 +22218,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.5464098073555166</t>
+          <t>0.5456171735241503</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -21770,17 +22322,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>561.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -21800,12 +22352,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.5462478184991274</t>
+          <t>0.5436720142602496</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -21857,17 +22409,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>573.0</t>
+          <t>561.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -21907,7 +22459,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Original Reference/Tohama I rooted analysis retained as comparability sensitivity.</t>
+          <t>Original Reference/Tohama I rooted unpruned tree retained as comparability sensitivity.</t>
         </is>
       </c>
     </row>
@@ -21978,7 +22530,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Fitch restricted to branches with support &gt;= 70 on the unpruned comparability frame</t>
+          <t>Unpruned comparability tree with Fitch origins restricted to branches with support &gt;=70.</t>
         </is>
       </c>
     </row>
@@ -22049,7 +22601,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Fitch restricted to branches with support &gt;= 90 on the unpruned comparability frame</t>
+          <t>Unpruned comparability tree with Fitch origins restricted to branches with support &gt;=90.</t>
         </is>
       </c>
     </row>
@@ -22155,7 +22707,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -22368,22 +22920,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.5462478184991274</t>
+          <t>0.5436720142602496</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -24742,260 +25294,275 @@
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
+          <t>resampling_inference_scope</t>
+        </is>
+      </c>
+      <c r="P86" s="1" t="inlineStr">
+        <is>
+          <t>block_assignment_metadata_source</t>
+        </is>
+      </c>
+      <c r="Q86" s="1" t="inlineStr">
+        <is>
+          <t>block_assignment_inventory_source</t>
+        </is>
+      </c>
+      <c r="R86" s="1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="P86" s="1" t="inlineStr">
+      <c r="S86" s="1" t="inlineStr">
         <is>
           <t>n_replicates</t>
         </is>
       </c>
-      <c r="Q86" s="1" t="inlineStr">
+      <c r="T86" s="1" t="inlineStr">
         <is>
           <t>tip_count_median</t>
         </is>
       </c>
-      <c r="R86" s="1" t="inlineStr">
+      <c r="U86" s="1" t="inlineStr">
         <is>
           <t>tip_count_min</t>
         </is>
       </c>
-      <c r="S86" s="1" t="inlineStr">
+      <c r="V86" s="1" t="inlineStr">
         <is>
           <t>tip_count_max</t>
         </is>
       </c>
-      <c r="T86" s="1" t="inlineStr">
+      <c r="W86" s="1" t="inlineStr">
         <is>
           <t>tip_count_q25</t>
         </is>
       </c>
-      <c r="U86" s="1" t="inlineStr">
+      <c r="X86" s="1" t="inlineStr">
         <is>
           <t>tip_count_q75</t>
         </is>
       </c>
-      <c r="V86" s="1" t="inlineStr">
+      <c r="Y86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_median</t>
         </is>
       </c>
-      <c r="W86" s="1" t="inlineStr">
+      <c r="Z86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_min</t>
         </is>
       </c>
-      <c r="X86" s="1" t="inlineStr">
+      <c r="AA86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_max</t>
         </is>
       </c>
-      <c r="Y86" s="1" t="inlineStr">
+      <c r="AB86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_q25</t>
         </is>
       </c>
-      <c r="Z86" s="1" t="inlineStr">
+      <c r="AC86" s="1" t="inlineStr">
         <is>
           <t>disrupted_tip_count_q75</t>
         </is>
       </c>
-      <c r="AA86" s="1" t="inlineStr">
+      <c r="AD86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_median</t>
         </is>
       </c>
-      <c r="AB86" s="1" t="inlineStr">
+      <c r="AE86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_min</t>
         </is>
       </c>
-      <c r="AC86" s="1" t="inlineStr">
+      <c r="AF86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_max</t>
         </is>
       </c>
-      <c r="AD86" s="1" t="inlineStr">
+      <c r="AG86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_q25</t>
         </is>
       </c>
-      <c r="AE86" s="1" t="inlineStr">
+      <c r="AH86" s="1" t="inlineStr">
         <is>
           <t>sampled_country_count_q75</t>
         </is>
       </c>
-      <c r="AF86" s="1" t="inlineStr">
+      <c r="AI86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_median</t>
         </is>
       </c>
-      <c r="AG86" s="1" t="inlineStr">
+      <c r="AJ86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_min</t>
         </is>
       </c>
-      <c r="AH86" s="1" t="inlineStr">
+      <c r="AK86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_max</t>
         </is>
       </c>
-      <c r="AI86" s="1" t="inlineStr">
+      <c r="AL86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_q25</t>
         </is>
       </c>
-      <c r="AJ86" s="1" t="inlineStr">
+      <c r="AM86" s="1" t="inlineStr">
         <is>
           <t>sampled_time_bin_count_q75</t>
         </is>
       </c>
-      <c r="AK86" s="1" t="inlineStr">
+      <c r="AN86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_median</t>
         </is>
       </c>
-      <c r="AL86" s="1" t="inlineStr">
+      <c r="AO86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_min</t>
         </is>
       </c>
-      <c r="AM86" s="1" t="inlineStr">
+      <c r="AP86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_max</t>
         </is>
       </c>
-      <c r="AN86" s="1" t="inlineStr">
+      <c r="AQ86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_q25</t>
         </is>
       </c>
-      <c r="AO86" s="1" t="inlineStr">
+      <c r="AR86" s="1" t="inlineStr">
         <is>
           <t>sampled_study_block_count_q75</t>
         </is>
       </c>
-      <c r="AP86" s="1" t="inlineStr">
+      <c r="AS86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_median</t>
         </is>
       </c>
-      <c r="AQ86" s="1" t="inlineStr">
+      <c r="AT86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_min</t>
         </is>
       </c>
-      <c r="AR86" s="1" t="inlineStr">
+      <c r="AU86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_max</t>
         </is>
       </c>
-      <c r="AS86" s="1" t="inlineStr">
+      <c r="AV86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_q25</t>
         </is>
       </c>
-      <c r="AT86" s="1" t="inlineStr">
+      <c r="AW86" s="1" t="inlineStr">
         <is>
           <t>sampled_subblock_count_q75</t>
         </is>
       </c>
-      <c r="AU86" s="1" t="inlineStr">
+      <c r="AX86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_median</t>
         </is>
       </c>
-      <c r="AV86" s="1" t="inlineStr">
+      <c r="AY86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_min</t>
         </is>
       </c>
-      <c r="AW86" s="1" t="inlineStr">
+      <c r="AZ86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_max</t>
         </is>
       </c>
-      <c r="AX86" s="1" t="inlineStr">
+      <c r="BA86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_q25</t>
         </is>
       </c>
-      <c r="AY86" s="1" t="inlineStr">
+      <c r="BB86" s="1" t="inlineStr">
         <is>
           <t>fitch_origin_events_q75</t>
         </is>
       </c>
-      <c r="AZ86" s="1" t="inlineStr">
+      <c r="BC86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_median</t>
         </is>
       </c>
-      <c r="BA86" s="1" t="inlineStr">
+      <c r="BD86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_min</t>
         </is>
       </c>
-      <c r="BB86" s="1" t="inlineStr">
+      <c r="BE86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_max</t>
         </is>
       </c>
-      <c r="BC86" s="1" t="inlineStr">
+      <c r="BF86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_q25</t>
         </is>
       </c>
-      <c r="BD86" s="1" t="inlineStr">
+      <c r="BG86" s="1" t="inlineStr">
         <is>
           <t>pastml_origin_events_q75</t>
         </is>
       </c>
-      <c r="BE86" s="1" t="inlineStr">
+      <c r="BH86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_median</t>
         </is>
       </c>
-      <c r="BF86" s="1" t="inlineStr">
+      <c r="BI86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_min</t>
         </is>
       </c>
-      <c r="BG86" s="1" t="inlineStr">
+      <c r="BJ86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_max</t>
         </is>
       </c>
-      <c r="BH86" s="1" t="inlineStr">
+      <c r="BK86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_q25</t>
         </is>
       </c>
-      <c r="BI86" s="1" t="inlineStr">
+      <c r="BL86" s="1" t="inlineStr">
         <is>
           <t>pastml_strict_origin_events_q75</t>
         </is>
       </c>
-      <c r="BJ86" s="1" t="inlineStr">
+      <c r="BM86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_median</t>
         </is>
       </c>
-      <c r="BK86" s="1" t="inlineStr">
+      <c r="BN86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_min</t>
         </is>
       </c>
-      <c r="BL86" s="1" t="inlineStr">
+      <c r="BO86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_max</t>
         </is>
       </c>
-      <c r="BM86" s="1" t="inlineStr">
+      <c r="BP86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_q25</t>
         </is>
       </c>
-      <c r="BN86" s="1" t="inlineStr">
+      <c r="BQ86" s="1" t="inlineStr">
         <is>
           <t>pastml_compatible_origin_events_q75</t>
         </is>
@@ -25039,12 +25606,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -25074,12 +25641,24 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
@@ -25128,6 +25707,9 @@
       <c r="BL87" t="inlineStr"/>
       <c r="BM87" t="inlineStr"/>
       <c r="BN87" t="inlineStr"/>
+      <c r="BO87" t="inlineStr"/>
+      <c r="BP87" t="inlineStr"/>
+      <c r="BQ87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -25167,12 +25749,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -25202,12 +25784,24 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
@@ -25256,6 +25850,9 @@
       <c r="BL88" t="inlineStr"/>
       <c r="BM88" t="inlineStr"/>
       <c r="BN88" t="inlineStr"/>
+      <c r="BO88" t="inlineStr"/>
+      <c r="BP88" t="inlineStr"/>
+      <c r="BQ88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -25295,12 +25892,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -25330,12 +25927,24 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
@@ -25384,6 +25993,9 @@
       <c r="BL89" t="inlineStr"/>
       <c r="BM89" t="inlineStr"/>
       <c r="BN89" t="inlineStr"/>
+      <c r="BO89" t="inlineStr"/>
+      <c r="BP89" t="inlineStr"/>
+      <c r="BQ89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -25423,12 +26035,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -25458,12 +26070,24 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
@@ -25512,6 +26136,9 @@
       <c r="BL90" t="inlineStr"/>
       <c r="BM90" t="inlineStr"/>
       <c r="BN90" t="inlineStr"/>
+      <c r="BO90" t="inlineStr"/>
+      <c r="BP90" t="inlineStr"/>
+      <c r="BQ90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -25551,12 +26178,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -25586,12 +26213,24 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
@@ -25640,6 +26279,9 @@
       <c r="BL91" t="inlineStr"/>
       <c r="BM91" t="inlineStr"/>
       <c r="BN91" t="inlineStr"/>
+      <c r="BO91" t="inlineStr"/>
+      <c r="BP91" t="inlineStr"/>
+      <c r="BQ91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -25679,12 +26321,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -25714,12 +26356,24 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
@@ -25768,6 +26422,9 @@
       <c r="BL92" t="inlineStr"/>
       <c r="BM92" t="inlineStr"/>
       <c r="BN92" t="inlineStr"/>
+      <c r="BO92" t="inlineStr"/>
+      <c r="BP92" t="inlineStr"/>
+      <c r="BQ92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -25807,12 +26464,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -25842,12 +26499,24 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
@@ -25896,6 +26565,9 @@
       <c r="BL93" t="inlineStr"/>
       <c r="BM93" t="inlineStr"/>
       <c r="BN93" t="inlineStr"/>
+      <c r="BO93" t="inlineStr"/>
+      <c r="BP93" t="inlineStr"/>
+      <c r="BQ93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -25935,12 +26607,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -25970,12 +26642,24 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
@@ -26024,6 +26708,9 @@
       <c r="BL94" t="inlineStr"/>
       <c r="BM94" t="inlineStr"/>
       <c r="BN94" t="inlineStr"/>
+      <c r="BO94" t="inlineStr"/>
+      <c r="BP94" t="inlineStr"/>
+      <c r="BQ94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -26063,12 +26750,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -26098,12 +26785,24 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
@@ -26152,6 +26851,9 @@
       <c r="BL95" t="inlineStr"/>
       <c r="BM95" t="inlineStr"/>
       <c r="BN95" t="inlineStr"/>
+      <c r="BO95" t="inlineStr"/>
+      <c r="BP95" t="inlineStr"/>
+      <c r="BQ95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -26191,12 +26893,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -26226,12 +26928,24 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
@@ -26280,6 +26994,9 @@
       <c r="BL96" t="inlineStr"/>
       <c r="BM96" t="inlineStr"/>
       <c r="BN96" t="inlineStr"/>
+      <c r="BO96" t="inlineStr"/>
+      <c r="BP96" t="inlineStr"/>
+      <c r="BQ96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -26310,260 +27027,275 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1842;representativeness_stress_test_only_not_unbiased_population_resample</t>
+          <t>diagnostic_stress_test_not_unbiased_population_resample</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
+          <t>active_manifest_only</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>archived_inventory_not_used</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>seed=20262408;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262409;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262410;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262411;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262412;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262413;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262414;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262415;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262416;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample;seed=20262417;country_cap=10;time_cap=10;selected_tip_count=1845;representativeness_stress_test_only_not_unbiased_population_resample</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="U97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="V97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>1842.0</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>552.0</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AD97" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AE97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
+      <c r="AF97" t="inlineStr">
         <is>
           <t>26.0</t>
         </is>
       </c>
-      <c r="AD97" t="inlineStr">
+      <c r="AG97" t="inlineStr">
         <is>
           <t>23.25</t>
         </is>
       </c>
-      <c r="AE97" t="inlineStr">
+      <c r="AH97" t="inlineStr">
         <is>
           <t>25.75</t>
         </is>
       </c>
-      <c r="AF97" t="inlineStr">
+      <c r="AI97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AG97" t="inlineStr">
+      <c r="AJ97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AH97" t="inlineStr">
+      <c r="AK97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AI97" t="inlineStr">
+      <c r="AL97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AJ97" t="inlineStr">
+      <c r="AM97" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>1716.0</t>
-        </is>
-      </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>1716.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>1716.0</t>
+          <t>1711.0</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1715.0</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1714.0</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1794.0</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>1827.0</t>
+          <t>1788.0</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
+          <t>1797.0</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>1792.25</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>1794.75</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AV97" t="inlineStr">
+      <c r="AY97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AW97" t="inlineStr">
+      <c r="AZ97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
+      <c r="BA97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AY97" t="inlineStr">
+      <c r="BB97" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
+      <c r="BC97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BA97" t="inlineStr">
+      <c r="BD97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BB97" t="inlineStr">
+      <c r="BE97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BC97" t="inlineStr">
+      <c r="BF97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BD97" t="inlineStr">
+      <c r="BG97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BE97" t="inlineStr">
+      <c r="BH97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BF97" t="inlineStr">
+      <c r="BI97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BG97" t="inlineStr">
+      <c r="BJ97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BH97" t="inlineStr">
+      <c r="BK97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BI97" t="inlineStr">
+      <c r="BL97" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="BJ97" t="inlineStr">
+      <c r="BM97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BK97" t="inlineStr">
+      <c r="BN97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BL97" t="inlineStr">
+      <c r="BO97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BM97" t="inlineStr">
+      <c r="BP97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BN97" t="inlineStr">
+      <c r="BQ97" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
